--- a/Test upload format/MSME/Recovery Upload.xlsx
+++ b/Test upload format/MSME/Recovery Upload.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>CGPAN</t>
   </si>
@@ -41,28 +41,22 @@
     <t>RecoveryDate</t>
   </si>
   <si>
-    <t>CGMSMGEN1609202500285827</t>
+    <t>CGMSMGEN2109202600357116</t>
   </si>
   <si>
-    <t>LWDM131</t>
+    <t>QAMSME18</t>
   </si>
   <si>
-    <t>CGMSMGEN1609202500285826</t>
+    <t>CGMSMGEN2109202600357117</t>
   </si>
   <si>
-    <t>LWDM130</t>
+    <t>QAMSME17</t>
   </si>
   <si>
-    <t>CGMSMGEN1609202500285830</t>
+    <t>CGMSMGEN2109202600357118</t>
   </si>
   <si>
-    <t>LWDM13</t>
-  </si>
-  <si>
-    <t>CGMSMGEN1609202500285829</t>
-  </si>
-  <si>
-    <t>LWDM133</t>
+    <t>QAMSME16</t>
   </si>
   <si>
     <t xml:space="preserve">        </t>
@@ -247,7 +241,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,7 +432,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -452,7 +446,22 @@
       <top style="thin">
         <color theme="4"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -577,7 +586,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -589,34 +598,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -701,7 +710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -710,9 +719,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1031,9 +1042,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.2190476190476" customWidth="1"/>
     <col min="2" max="2" width="27.1428571428571" customWidth="1"/>
@@ -1042,7 +1053,7 @@
     <col min="6" max="6" width="14.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1056,66 +1067,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C2">
-        <v>800000000</v>
-      </c>
-      <c r="D2" s="5">
-        <v>46368</v>
+        <v>80000000</v>
+      </c>
+      <c r="D2" s="6">
+        <v>47829</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>800000000</v>
-      </c>
-      <c r="D3" s="5">
-        <v>46368</v>
-      </c>
-      <c r="F3" s="5"/>
+        <v>80000000</v>
+      </c>
+      <c r="D3" s="6">
+        <v>47829</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>800000000</v>
-      </c>
-      <c r="D4" s="5">
+        <v>80000000</v>
+      </c>
+      <c r="D4" s="6">
         <v>47829</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>800000000</v>
-      </c>
-      <c r="D5" s="5">
-        <v>47829</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
